--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0091.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0091.xlsx
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>GÌ CƠ?! Đ-Đợi đã! T-Ta cảm thấy một sức mạnh bí ẩn đang trỗi dậy trong người! Ta khỏi rồi! Hoàn toàn khỏi rồi!</t>
+          <t>GÌ CƠ?! Đ-Đợi đã! T-Tao cảm thấy một sức mạnh bí ẩn đang trỗi dậy trong người! Tao khỏi rồi! Hoàn toàn khỏi rồi!</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hít... Ta cứ tưởng... ta tưởng tụi mình đã đánh bại Threnodian rồi...</t>
+          <t>Hít... Tao cứ tưởng... tao tưởng tụi mình đã đánh bại Threnodian rồi...</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Ghi chú khác: BÃO HƯ VÔ! TRẢ BÀI LUẬN CỦA TA ĐÂY! TA VỚI Ngươi CHƯA XONG ĐÂU AAAAAHHHH—!!!</t>
+          <t>Ghi chú khác: BÃO HƯ VÔ! TRẢ BÀI LUẬN CỦA TA ĐÂY! TA VỚI MÀY CHƯA XONG ĐÂU AAAAAHHHH—!!!</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Không, không, người này khác đấy! {Male=Quá khứ;Female=Quá khứ} của {Male=anh ấy;Female=chị ấy} bí ẩn lắm…</t>
+          <t>Không, không, người này khác đấy! {Male=His;Female=Her} của {Male=anh ấy;Female=chị ấy} bí ẩn lắm…</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Có người bảo {Male=hắn;Female=cô ta} dính líu đến vụ Threnody hồi sinh ở Jinzhou và Rinascita. Đúng là "nam châm rắc rối" mà.</t>
+          <t>Có người bảo {Male=he;Female=she} dính líu đến vụ Threnody hồi sinh ở Jinzhou và Rinascita. Đúng là "nam châm rắc rối" mà.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ngon! Anh bạn, hồi nhỏ Roya cậu toàn ăn Fruit Crackle à? Sướng thật đấy!</t>
+          <t>Ngon! Anh bạn, hồi nhỏ Roya mày toàn ăn Fruit Crackle à? Sướng thật đấy!</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Ê, sao cậu có thể nói chuyện với mẹ... không, là *mẹ của tụi mình* như vậy hả? Mẹ ơi! Lại đây! Để con dẫn mẹ đi tham quan trường!</t>
+          <t>Ê, sao mày có thể nói chuyện với mẹ... không, là *mẹ của tụi mình* như vậy hả? Mẹ ơi! Lại đây! Để con dẫn mẹ đi tham quan trường!</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vậy cô ấy thích gì nhỉ? Ta nên nghĩ ra vài sở thích chung trước khi tiếp cận cô ấy, phải không?</t>
+          <t>Vậy cô ấy thích gì nhỉ? Tao nên nghĩ ra vài sở thích chung trước khi tiếp cận cô ấy, phải không?</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Hừm, có lẽ cậu nói đúng... À khoan, giờ ta hiểu rồi!</t>
+          <t>Hừm, có lẽ cậu nói đúng... À khoan, giờ tao hiểu rồi!</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Có lẽ tiến bộ vốn dĩ là một vòng xoáy, chứ không phải đường thẳng. Chán nản làm gì chứ? Viết lại toàn bộ à? Cứ đem tới đây! Ta làm được mà!</t>
+          <t>Có lẽ tiến bộ vốn dĩ là một vòng xoáy, chứ không phải đường thẳng. Chán nản làm gì chứ? Viết lại toàn bộ à? Cứ đem tới đây! Tao làm được mà!</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>À, xin chào! Chắc hẳn cậu là Rover phải không? Không ngờ lại gặp cậu ở đây.</t>
+          <t>À, xin chào! Chắc hẳn cậu là Vận Mệnh Giả phải không? Không ngờ lại gặp cậu ở đây.</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Ta không biết điều gì đưa cậu đến đây, nhưng hãy tận hưởng thời gian của mình nhé. Nếu cậu muốn học gì, hãy tìm ta ở Kho Lưu Trữ!</t>
+          <t>Tao không biết điều gì đưa cậu đến đây, nhưng hãy tận hưởng thời gian của mình nhé. Nếu cậu muốn học gì, hãy tìm tao ở Kho Lưu Trữ!</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Này! Đừng có mà ngất xỉu với ta chứ!!</t>
+          <t>Này! Đừng có mà ngất xỉu với tao chứ!!</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ugh, "Những điều cơ bản về Bảo mật Thông tin"... Lớp học vớ vẩn. Ta thà ở phòng thí nghiệm làm việc thực tế còn hơn.</t>
+          <t>Ugh, "Những điều cơ bản về Bảo mật Thông tin"... Lớp học vớ vẩn. Tao thà ở phòng thí nghiệm làm việc thực tế còn hơn.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Thấy chưa? Đến một tân binh còn hiểu hơn cậu! Cậu... {PlayerName} phải không? Ta thích tinh thần hoài nghi mà tò mò của cậu đấy. Cậu được lắm!</t>
+          <t>Thấy chưa? Đến một tân binh còn hiểu hơn cậu! Cậu... {PlayerName} phải không? Tao thích tinh thần hoài nghi mà tò mò của cậu đấy. Cậu được lắm!</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hôm nay ta chẳng học được cái gì cả...</t>
+          <t>Hôm nay tao chẳng học được cái gì cả...</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Ba ngày rồi ta chưa ăn gì... phải tiếp tục thôi...</t>
+          <t>Ba ngày rồi tao chưa ăn gì... phải tiếp tục thôi...</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Để dành chút đồ ăn cho ta khi ta về nhé. Gì cũng được, ta không kén đâu!</t>
+          <t>Để dành chút đồ ăn cho tao khi tao về nhé. Gì cũng được, tao không kén đâu!</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Thôi bỏ đi, ta sẽ gọi "món đặc biệt hôm nay" vậy!</t>
+          <t>Thôi bỏ đi, tao sẽ gọi "món đặc biệt hôm nay" vậy!</t>
         </is>
       </c>
     </row>
